--- a/RTNValidation.xlsx
+++ b/RTNValidation.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="12">
   <si>
     <t>RTN</t>
   </si>
@@ -474,10 +474,10 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="1">
         <v>11</v>
       </c>
     </row>
@@ -488,10 +488,10 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="1">
         <v>11</v>
       </c>
     </row>
@@ -502,10 +502,10 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="1">
         <v>11</v>
       </c>
     </row>
